--- a/artfynd/A 22081-2026 artfynd.xlsx
+++ b/artfynd/A 22081-2026 artfynd.xlsx
@@ -675,73 +675,69 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122685767</v>
+        <v>128629713</v>
       </c>
       <c r="B2" t="n">
-        <v>56688</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56822</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>100086</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dammfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Myotis dasycneme</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(F.Boie, 1825)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>autobox</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hultetvägen, Grytsjön, Kråksmåla, Sm</t>
+          <t>Hultetvägen, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>547071</v>
+        <v>547055</v>
       </c>
       <c r="R2" t="n">
-        <v>6321793</v>
+        <v>6321797</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,27 +761,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Spåren fanns inte i förrgår, så max 2 dagar gamla</t>
+          <t>wurb2024 AA-43 med Pettersson u384</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -812,69 +808,68 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128629713</v>
+        <v>122685767</v>
       </c>
       <c r="B3" t="n">
-        <v>56772</v>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100086</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dammfladdermus</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Myotis dasycneme</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(F.Boie, 1825)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>autobox</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hultetvägen, Sm</t>
+          <t>Hultetvägen, Grytsjön, Kråksmåla, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>547055</v>
+        <v>547071</v>
       </c>
       <c r="R3" t="n">
-        <v>6321797</v>
+        <v>6321793</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -898,27 +893,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>wurb2024 AA-43 med Pettersson u384</t>
+          <t>Spåren fanns inte i förrgår, så max 2 dagar gamla</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -948,7 +943,7 @@
         <v>128629718</v>
       </c>
       <c r="B4" t="n">
-        <v>56610</v>
+        <v>56835</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1078,10 +1073,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128629715</v>
+        <v>128629716</v>
       </c>
       <c r="B5" t="n">
-        <v>56612</v>
+        <v>56816</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1089,26 +1084,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>206002</v>
+        <v>205998</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1211,10 +1206,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128629716</v>
+        <v>128629715</v>
       </c>
       <c r="B6" t="n">
-        <v>56591</v>
+        <v>56837</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,26 +1217,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>205998</v>
+        <v>206002</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">

--- a/artfynd/A 22081-2026 artfynd.xlsx
+++ b/artfynd/A 22081-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -805,6 +810,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128629713</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -937,6 +947,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122685767</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1070,6 +1085,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128629718</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1203,6 +1223,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128629716</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1336,8 +1361,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128629715</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>